--- a/Docs/01_db/テーブル定義.xlsx
+++ b/Docs/01_db/テーブル定義.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CAFC385-ADD6-4DA7-8D41-8192379D1131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9FEB99-825F-471C-9F8D-7D27A6BD5C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{596F7F7F-6EFA-44D5-8725-F1D23DCA1A6A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="29">
   <si>
     <t>社員テーブル</t>
     <rPh sb="0" eb="2">
@@ -148,6 +148,74 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勤務地</t>
+    <rPh sb="0" eb="3">
+      <t>キンムチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>gender</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>性別</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>性別番号</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勤務地番号</t>
+    <rPh sb="0" eb="3">
+      <t>キンムチ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>性別番号</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>gender_id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>area_id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勤務地テーブル</t>
+    <rPh sb="0" eb="3">
+      <t>キンムチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>性別テーブル</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -560,10 +628,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B64056ED-A479-42EE-97CC-42CDA63294E7}">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="6" max="6" width="9.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.08203125" customWidth="1"/>
     <col min="15" max="15" width="9.9140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -679,10 +748,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
@@ -691,7 +760,151 @@
       <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Docs/01_db/テーブル定義.xlsx
+++ b/Docs/01_db/テーブル定義.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9FEB99-825F-471C-9F8D-7D27A6BD5C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB42CF4-FB77-439B-9520-188238DD0FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{596F7F7F-6EFA-44D5-8725-F1D23DCA1A6A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
   <si>
     <t>社員テーブル</t>
     <rPh sb="0" eb="2">
@@ -99,10 +99,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>int</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>name</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -117,10 +113,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>string</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>dept_id</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -217,6 +209,21 @@
     <rPh sb="0" eb="2">
       <t>セイベツ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桁</t>
+    <rPh sb="0" eb="1">
+      <t>ケタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>integer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>character varying</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -241,7 +248,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,8 +261,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -278,13 +291,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -292,6 +314,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -628,23 +656,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B64056ED-A479-42EE-97CC-42CDA63294E7}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
+    <col min="5" max="5" width="15.5" customWidth="1"/>
     <col min="6" max="6" width="9.83203125" customWidth="1"/>
     <col min="11" max="11" width="10.08203125" customWidth="1"/>
     <col min="15" max="15" width="9.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="J1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -663,6 +692,9 @@
       <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="J2" s="2" t="s">
         <v>1</v>
       </c>
@@ -681,8 +713,11 @@
       <c r="O2" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="P2" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -693,118 +728,143 @@
         <v>9</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
+      <c r="E3" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="G3" s="1">
+        <v>3</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="1"/>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="1">
+        <f>G6</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
+      <c r="E4" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G4" s="1">
+        <v>20</v>
+      </c>
       <c r="J4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1" t="s">
-        <v>13</v>
+      <c r="N4" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="P4" s="1">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
+      <c r="E5" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
       <c r="J5" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>10</v>
+      <c r="N5" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="P5" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>10</v>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="F6" s="1"/>
+      <c r="G6" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="E7" s="4"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
@@ -823,6 +883,9 @@
       <c r="F10" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="G10" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="J10" s="2" t="s">
         <v>1</v>
       </c>
@@ -841,69 +904,86 @@
       <c r="O10" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="P10" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
-        <v>10</v>
+      <c r="E11" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="G11" s="1">
+        <f>G5</f>
+        <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="M11" s="1"/>
-      <c r="N11" s="1" t="s">
-        <v>10</v>
+      <c r="N11" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="P11" s="1">
+        <f>P5</f>
+        <v>2</v>
+      </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="1" t="s">
-        <v>13</v>
+      <c r="E12" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G12" s="1">
+        <v>5</v>
+      </c>
       <c r="J12" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="1" t="s">
-        <v>13</v>
+      <c r="N12" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="P12" s="1">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -913,6 +993,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100F53224CB4AB7E84C876E95102DDD2B7D" ma:contentTypeVersion="4" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="341b165d7395d9e1ee8f0503b074b01e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="35ae0af6-260d-49f6-9ae2-0fef1c1b6caa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5f4d16edb58affd9be284592f237857a" ns3:_="">
     <xsd:import namespace="35ae0af6-260d-49f6-9ae2-0fef1c1b6caa"/>
@@ -1056,7 +1142,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1065,13 +1151,23 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{650F825D-0105-45F1-88FF-B12167E9AF70}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="35ae0af6-260d-49f6-9ae2-0fef1c1b6caa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBA22361-F10E-463F-9771-E2076C8AD685}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1089,26 +1185,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0630FC3D-4C9B-4075-A151-5DB318A32CEE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{650F825D-0105-45F1-88FF-B12167E9AF70}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="35ae0af6-260d-49f6-9ae2-0fef1c1b6caa"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>